--- a/ESM/eval_results/lgbm_esm_result.xlsx
+++ b/ESM/eval_results/lgbm_esm_result.xlsx
@@ -546,22 +546,22 @@
         <v>0.132</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9987</v>
+        <v>0.9974</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
+        <v>0.3273</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6667</v>
+        <v>0.4932</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6369</v>
+        <v>0.5153</v>
       </c>
     </row>
   </sheetData>
